--- a/Precificação.xlsx
+++ b/Precificação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\labsfiap\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C503D5F3-08A4-4FE7-A911-C2C39CB67911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE0DBDF-1DC0-4EDB-A1A8-09F3C98545D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{78B45F45-2F96-4A6A-AFE3-9BAC80B0CE9C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Kit do chassi</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Sensor Ultrassonico</t>
   </si>
 </sst>
 </file>
@@ -488,12 +491,20 @@
         <v>22.39</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+    </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>146.16999999999999</v>
+        <v>165.17</v>
       </c>
     </row>
   </sheetData>
